--- a/priv/python/excel_templates/TEMPLATE_Mud Resistivity.xlsx
+++ b/priv/python/excel_templates/TEMPLATE_Mud Resistivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SUNCOR OB300 FIREBAG 9-13-95-6\Well Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deanerfree/projects/elixir/suncor-project-spinup/priv/python/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C23D5B-5597-4E74-ABC3-15403AC4609D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD47D6-7052-CB42-9C17-CE058E148B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="760" windowWidth="16240" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9360" yWindow="760" windowWidth="16240" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mud Resistivity" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Mud Resistivity Test</t>
   </si>
@@ -60,27 +60,6 @@
   </si>
   <si>
     <t>mS/Cm</t>
-  </si>
-  <si>
-    <t>SUNCOR OB300 FIREBAG 9-13-95-6</t>
-  </si>
-  <si>
-    <t>1AB/09-13-095-06W4/0</t>
-  </si>
-  <si>
-    <t>TD</t>
-  </si>
-  <si>
-    <t>Added 1/4 bag of salt.</t>
-  </si>
-  <si>
-    <t>Within parameters.</t>
-  </si>
-  <si>
-    <t>Added 1/3 bag of salt, within parameters.</t>
-  </si>
-  <si>
-    <t>Water added to the system during sweep. Within parameters.</t>
   </si>
 </sst>
 </file>
@@ -798,16 +777,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:6" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:6" ht="22" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
@@ -819,27 +798,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="20" t="s">
-        <v>8</v>
-      </c>
+    <row r="3" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="22"/>
       <c r="F3" s="27"/>
     </row>
-    <row r="4" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="20" t="s">
-        <v>9</v>
-      </c>
+    <row r="4" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
       <c r="D4" s="21"/>
       <c r="E4" s="22"/>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,215 +834,135 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="8">
-        <v>100</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="B6" s="8"/>
+      <c r="C6" s="11" t="str">
         <f>IF(F6="","",(10/F6))</f>
-        <v>1.8939393939393938</v>
-      </c>
-      <c r="D6" s="8">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10">
-        <v>5.28</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>2</v>
       </c>
-      <c r="B7" s="6">
-        <v>150</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="B7" s="6"/>
+      <c r="C7" s="11" t="str">
         <f t="shared" ref="C7:C15" si="0">IF(F7="","",(10/F7))</f>
-        <v>3.0303030303030303</v>
-      </c>
-      <c r="D7" s="6">
-        <v>18.2</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4">
-        <v>3.3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>3</v>
       </c>
-      <c r="B8" s="6">
-        <v>154</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="6"/>
+      <c r="C8" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>2.5</v>
-      </c>
-      <c r="D8" s="12">
-        <v>18</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="4">
-        <v>4</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>4</v>
       </c>
-      <c r="B9" s="16">
-        <v>180</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="B9" s="16"/>
+      <c r="C9" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>2.2573363431151243</v>
-      </c>
-      <c r="D9" s="6">
-        <v>23.2</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="17">
-        <v>4.43</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="17"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>5</v>
       </c>
-      <c r="B10" s="6">
-        <v>205</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="6"/>
+      <c r="C10" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>2.109704641350211</v>
-      </c>
-      <c r="D10" s="6">
-        <v>20.3</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="17">
-        <v>4.74</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="17"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>6</v>
       </c>
-      <c r="B11" s="6">
-        <v>222</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="B11" s="6"/>
+      <c r="C11" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>1.8867924528301887</v>
-      </c>
-      <c r="D11" s="18">
-        <v>20</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="17">
-        <v>5.3</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="17"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>7</v>
       </c>
-      <c r="B12" s="6">
-        <v>238</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="B12" s="6"/>
+      <c r="C12" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>2.5773195876288661</v>
-      </c>
-      <c r="D12" s="18">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="17">
-        <v>3.88</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>8</v>
       </c>
-      <c r="B13" s="6">
-        <v>272</v>
-      </c>
-      <c r="C13" s="11">
+      <c r="B13" s="6"/>
+      <c r="C13" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>1.8281535648994516</v>
-      </c>
-      <c r="D13" s="3">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="17">
-        <v>5.47</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="17"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>9</v>
       </c>
-      <c r="B14" s="3">
-        <v>322</v>
-      </c>
-      <c r="C14" s="11">
+      <c r="B14" s="3"/>
+      <c r="C14" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>2.0040080160320639</v>
-      </c>
-      <c r="D14" s="3">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="17">
-        <v>4.99</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="19">
+      <c r="B15" s="3"/>
+      <c r="C15" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>1.9083969465648853</v>
-      </c>
-      <c r="D15" s="3">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="17">
-        <v>5.24</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1093,15 +988,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007936CBEE0A456044BDA65122A5B0F5F8" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5d7b9cbce9364425416f89c8d3c2b0fb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a16e579-8e52-462c-b9fb-90fad13862ef" xmlns:ns3="f2e3cb03-81f0-44cd-9968-695b701ef7ef" xmlns:ns4="90a9caed-1441-4e6e-970c-7f1ae8660165" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ac0bef3ad4cc5a6152d7bbfb167c93" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="0a16e579-8e52-462c-b9fb-90fad13862ef"/>
@@ -1367,6 +1253,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25BF83A-C909-471D-9221-76FC2FF6A91B}">
   <ds:schemaRefs>
@@ -1379,14 +1274,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4031E4A-C623-40EE-ADF3-C462DD3BCCCE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ECEC2CC-0941-43C9-B656-667696CE4F28}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1406,6 +1293,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4031E4A-C623-40EE-ADF3-C462DD3BCCCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{235c080e-3229-4a2e-b702-e00c8f196752}" enabled="1" method="Standard" siteId="{1aa51068-11a6-4bd2-8646-1fff31a30ffc}" removed="0"/>
